--- a/results/progression_tables.xlsx
+++ b/results/progression_tables.xlsx
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.03815143084033142</v>
+        <v>0.03876631986076129</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.05192216674822492</v>
+        <v>0.05385701399555246</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7233485650541269</v>
+        <v>0.7309388127508656</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1408185877954547</v>
+        <v>0.1411503608120991</v>
       </c>
     </row>
     <row r="9">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.0492646869527586</v>
+        <v>0.05196436155638658</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.05549378139223062</v>
+        <v>0.06897455878346505</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.7653984125051525</v>
+        <v>0.764948239864317</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1418113364972837</v>
+        <v>0.1438814241622837</v>
       </c>
     </row>
   </sheetData>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.04535481935670799</v>
+        <v>0.04454464074078138</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.06874272004881311</v>
+        <v>0.0677524320293323</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7233669905942129</v>
+        <v>0.726127251608176</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1655042130905217</v>
+        <v>0.1660053146533527</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.06426797495960522</v>
+        <v>0.07243345303208561</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.07959012705326016</v>
+        <v>0.08027114897677987</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.7488585516725471</v>
+        <v>0.7500814076138312</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1714409040583956</v>
+        <v>0.1727661424262591</v>
       </c>
     </row>
   </sheetData>
